--- a/test_data/B2B_file2.xlsx
+++ b/test_data/B2B_file2.xlsx
@@ -6007,16 +6007,16 @@
         <v>1101.69</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>99.16</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>198.31</v>
+        <v>0</v>
       </c>
       <c r="AP3">
         <v>0</v>
@@ -6533,16 +6533,16 @@
         <v>169.49</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>15.26</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="AN5">
         <v>0</v>
       </c>
       <c r="AO5">
-        <v>30.51</v>
+        <v>0</v>
       </c>
       <c r="AP5">
         <v>0</v>
@@ -7053,16 +7053,16 @@
         <v>1271.19</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>114.41</v>
       </c>
       <c r="AN7">
         <v>0</v>
       </c>
       <c r="AO7">
-        <v>228.81</v>
+        <v>0</v>
       </c>
       <c r="AP7">
         <v>0</v>
@@ -8365,16 +8365,16 @@
         <v>1271.19</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>114.41</v>
       </c>
       <c r="AN12">
         <v>0</v>
       </c>
       <c r="AO12">
-        <v>228.81</v>
+        <v>0</v>
       </c>
       <c r="AP12">
         <v>0</v>
@@ -9671,16 +9671,16 @@
         <v>1101.69</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>99.16</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AN17">
         <v>0</v>
       </c>
       <c r="AO17">
-        <v>198.31</v>
+        <v>0</v>
       </c>
       <c r="AP17">
         <v>0</v>
@@ -9931,16 +9931,16 @@
         <v>1101.69</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>99.16</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AN18">
         <v>0</v>
       </c>
       <c r="AO18">
-        <v>198.31</v>
+        <v>0</v>
       </c>
       <c r="AP18">
         <v>0</v>
@@ -11237,16 +11237,16 @@
         <v>1694.92</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AN23">
         <v>0</v>
       </c>
       <c r="AO23">
-        <v>305.08</v>
+        <v>0</v>
       </c>
       <c r="AP23">
         <v>0</v>
@@ -11497,16 +11497,16 @@
         <v>1271.19</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>114.41</v>
       </c>
       <c r="AN24">
         <v>0</v>
       </c>
       <c r="AO24">
-        <v>228.81</v>
+        <v>0</v>
       </c>
       <c r="AP24">
         <v>0</v>
@@ -12277,16 +12277,16 @@
         <v>169.49</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>15.26</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="AN27">
         <v>0</v>
       </c>
       <c r="AO27">
-        <v>30.51</v>
+        <v>0</v>
       </c>
       <c r="AP27">
         <v>0</v>
@@ -14363,16 +14363,16 @@
         <v>423.73</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>38.14</v>
       </c>
       <c r="AM35">
-        <v>0</v>
+        <v>38.13</v>
       </c>
       <c r="AN35">
         <v>0</v>
       </c>
       <c r="AO35">
-        <v>76.27</v>
+        <v>0</v>
       </c>
       <c r="AP35">
         <v>0</v>
@@ -15403,16 +15403,16 @@
         <v>423.73</v>
       </c>
       <c r="AL39">
-        <v>0</v>
+        <v>38.14</v>
       </c>
       <c r="AM39">
-        <v>0</v>
+        <v>38.13</v>
       </c>
       <c r="AN39">
         <v>0</v>
       </c>
       <c r="AO39">
-        <v>76.27</v>
+        <v>0</v>
       </c>
       <c r="AP39">
         <v>0</v>
@@ -16461,16 +16461,16 @@
         <v>338.14</v>
       </c>
       <c r="AL43">
-        <v>0</v>
+        <v>30.43</v>
       </c>
       <c r="AM43">
-        <v>0</v>
+        <v>30.43</v>
       </c>
       <c r="AN43">
         <v>0</v>
       </c>
       <c r="AO43">
-        <v>60.86</v>
+        <v>0</v>
       </c>
       <c r="AP43">
         <v>0</v>
@@ -18033,16 +18033,16 @@
         <v>1101.69</v>
       </c>
       <c r="AL49">
-        <v>0</v>
+        <v>99.16</v>
       </c>
       <c r="AM49">
-        <v>0</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AN49">
         <v>0</v>
       </c>
       <c r="AO49">
-        <v>198.31</v>
+        <v>0</v>
       </c>
       <c r="AP49">
         <v>0</v>
@@ -18293,16 +18293,16 @@
         <v>1694.92</v>
       </c>
       <c r="AL50">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AM50">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AN50">
         <v>0</v>
       </c>
       <c r="AO50">
-        <v>305.08</v>
+        <v>0</v>
       </c>
       <c r="AP50">
         <v>0</v>
@@ -18553,16 +18553,16 @@
         <v>169.49</v>
       </c>
       <c r="AL51">
-        <v>0</v>
+        <v>15.26</v>
       </c>
       <c r="AM51">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="AN51">
         <v>0</v>
       </c>
       <c r="AO51">
-        <v>30.51</v>
+        <v>0</v>
       </c>
       <c r="AP51">
         <v>0</v>
@@ -18813,16 +18813,16 @@
         <v>1694.92</v>
       </c>
       <c r="AL52">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AM52">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AN52">
         <v>0</v>
       </c>
       <c r="AO52">
-        <v>305.08</v>
+        <v>0</v>
       </c>
       <c r="AP52">
         <v>0</v>
@@ -19599,16 +19599,16 @@
         <v>677.97</v>
       </c>
       <c r="AL55">
-        <v>0</v>
+        <v>61.02</v>
       </c>
       <c r="AM55">
-        <v>0</v>
+        <v>61.01</v>
       </c>
       <c r="AN55">
         <v>0</v>
       </c>
       <c r="AO55">
-        <v>122.03</v>
+        <v>0</v>
       </c>
       <c r="AP55">
         <v>0</v>
@@ -20905,16 +20905,16 @@
         <v>1352.54</v>
       </c>
       <c r="AL60">
-        <v>0</v>
+        <v>121.73</v>
       </c>
       <c r="AM60">
-        <v>0</v>
+        <v>121.73</v>
       </c>
       <c r="AN60">
         <v>0</v>
       </c>
       <c r="AO60">
-        <v>243.46</v>
+        <v>0</v>
       </c>
       <c r="AP60">
         <v>0</v>
@@ -22725,16 +22725,16 @@
         <v>2203.39</v>
       </c>
       <c r="AL67">
-        <v>0</v>
+        <v>198.3</v>
       </c>
       <c r="AM67">
-        <v>0</v>
+        <v>198.31</v>
       </c>
       <c r="AN67">
         <v>0</v>
       </c>
       <c r="AO67">
-        <v>396.61</v>
+        <v>0</v>
       </c>
       <c r="AP67">
         <v>0</v>
@@ -23505,16 +23505,16 @@
         <v>338.98</v>
       </c>
       <c r="AL70">
-        <v>0</v>
+        <v>30.51</v>
       </c>
       <c r="AM70">
-        <v>0</v>
+        <v>30.51</v>
       </c>
       <c r="AN70">
         <v>0</v>
       </c>
       <c r="AO70">
-        <v>61.02</v>
+        <v>0</v>
       </c>
       <c r="AP70">
         <v>0</v>
@@ -24811,16 +24811,16 @@
         <v>1694.92</v>
       </c>
       <c r="AL75">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AM75">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AN75">
         <v>0</v>
       </c>
       <c r="AO75">
-        <v>305.08</v>
+        <v>0</v>
       </c>
       <c r="AP75">
         <v>0</v>
@@ -25071,16 +25071,16 @@
         <v>550.85</v>
       </c>
       <c r="AL76">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AM76">
-        <v>0</v>
+        <v>49.57000000000001</v>
       </c>
       <c r="AN76">
         <v>0</v>
       </c>
       <c r="AO76">
-        <v>99.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP76">
         <v>0</v>
@@ -25597,16 +25597,16 @@
         <v>677.97</v>
       </c>
       <c r="AL78">
-        <v>0</v>
+        <v>61.02</v>
       </c>
       <c r="AM78">
-        <v>0</v>
+        <v>61.01</v>
       </c>
       <c r="AN78">
         <v>0</v>
       </c>
       <c r="AO78">
-        <v>122.03</v>
+        <v>0</v>
       </c>
       <c r="AP78">
         <v>0</v>
@@ -26377,16 +26377,16 @@
         <v>1271.19</v>
       </c>
       <c r="AL81">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AM81">
-        <v>0</v>
+        <v>114.41</v>
       </c>
       <c r="AN81">
         <v>0</v>
       </c>
       <c r="AO81">
-        <v>228.81</v>
+        <v>0</v>
       </c>
       <c r="AP81">
         <v>0</v>
@@ -26637,16 +26637,16 @@
         <v>1101.69</v>
       </c>
       <c r="AL82">
-        <v>0</v>
+        <v>99.16</v>
       </c>
       <c r="AM82">
-        <v>0</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AN82">
         <v>0</v>
       </c>
       <c r="AO82">
-        <v>198.31</v>
+        <v>0</v>
       </c>
       <c r="AP82">
         <v>0</v>
@@ -27943,16 +27943,16 @@
         <v>550.85</v>
       </c>
       <c r="AL87">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AM87">
-        <v>0</v>
+        <v>49.57000000000001</v>
       </c>
       <c r="AN87">
         <v>0</v>
       </c>
       <c r="AO87">
-        <v>99.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP87">
         <v>0</v>
@@ -28989,16 +28989,16 @@
         <v>2203.39</v>
       </c>
       <c r="AL91">
-        <v>0</v>
+        <v>198.3</v>
       </c>
       <c r="AM91">
-        <v>0</v>
+        <v>198.31</v>
       </c>
       <c r="AN91">
         <v>0</v>
       </c>
       <c r="AO91">
-        <v>396.61</v>
+        <v>0</v>
       </c>
       <c r="AP91">
         <v>0</v>
@@ -29249,16 +29249,16 @@
         <v>2203.39</v>
       </c>
       <c r="AL92">
-        <v>0</v>
+        <v>198.3</v>
       </c>
       <c r="AM92">
-        <v>0</v>
+        <v>198.31</v>
       </c>
       <c r="AN92">
         <v>0</v>
       </c>
       <c r="AO92">
-        <v>396.61</v>
+        <v>0</v>
       </c>
       <c r="AP92">
         <v>0</v>
@@ -29769,16 +29769,16 @@
         <v>1014.41</v>
       </c>
       <c r="AL94">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="AM94">
-        <v>0</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="AN94">
         <v>0</v>
       </c>
       <c r="AO94">
-        <v>182.59</v>
+        <v>0</v>
       </c>
       <c r="AP94">
         <v>0</v>
@@ -31855,16 +31855,16 @@
         <v>2203.39</v>
       </c>
       <c r="AL102">
-        <v>0</v>
+        <v>198.3</v>
       </c>
       <c r="AM102">
-        <v>0</v>
+        <v>198.31</v>
       </c>
       <c r="AN102">
         <v>0</v>
       </c>
       <c r="AO102">
-        <v>396.61</v>
+        <v>0</v>
       </c>
       <c r="AP102">
         <v>0</v>
@@ -32635,16 +32635,16 @@
         <v>677.97</v>
       </c>
       <c r="AL105">
-        <v>0</v>
+        <v>61.02</v>
       </c>
       <c r="AM105">
-        <v>0</v>
+        <v>61.01</v>
       </c>
       <c r="AN105">
         <v>0</v>
       </c>
       <c r="AO105">
-        <v>122.03</v>
+        <v>0</v>
       </c>
       <c r="AP105">
         <v>0</v>
@@ -33941,16 +33941,16 @@
         <v>1271.19</v>
       </c>
       <c r="AL110">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AM110">
-        <v>0</v>
+        <v>114.41</v>
       </c>
       <c r="AN110">
         <v>0</v>
       </c>
       <c r="AO110">
-        <v>228.81</v>
+        <v>0</v>
       </c>
       <c r="AP110">
         <v>0</v>
@@ -34201,16 +34201,16 @@
         <v>677.97</v>
       </c>
       <c r="AL111">
-        <v>0</v>
+        <v>61.02</v>
       </c>
       <c r="AM111">
-        <v>0</v>
+        <v>61.01</v>
       </c>
       <c r="AN111">
         <v>0</v>
       </c>
       <c r="AO111">
-        <v>122.03</v>
+        <v>0</v>
       </c>
       <c r="AP111">
         <v>0</v>
@@ -34981,16 +34981,16 @@
         <v>676.27</v>
       </c>
       <c r="AL114">
-        <v>0</v>
+        <v>60.86</v>
       </c>
       <c r="AM114">
-        <v>0</v>
+        <v>60.87</v>
       </c>
       <c r="AN114">
         <v>0</v>
       </c>
       <c r="AO114">
-        <v>121.73</v>
+        <v>0</v>
       </c>
       <c r="AP114">
         <v>0</v>
@@ -37321,16 +37321,16 @@
         <v>169.49</v>
       </c>
       <c r="AL123">
-        <v>0</v>
+        <v>15.26</v>
       </c>
       <c r="AM123">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="AN123">
         <v>0</v>
       </c>
       <c r="AO123">
-        <v>30.51</v>
+        <v>0</v>
       </c>
       <c r="AP123">
         <v>0</v>
@@ -38633,16 +38633,16 @@
         <v>550.85</v>
       </c>
       <c r="AL128">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AM128">
-        <v>0</v>
+        <v>49.57000000000001</v>
       </c>
       <c r="AN128">
         <v>0</v>
       </c>
       <c r="AO128">
-        <v>99.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP128">
         <v>0</v>
@@ -38893,16 +38893,16 @@
         <v>676.27</v>
       </c>
       <c r="AL129">
-        <v>0</v>
+        <v>60.86</v>
       </c>
       <c r="AM129">
-        <v>0</v>
+        <v>60.87</v>
       </c>
       <c r="AN129">
         <v>0</v>
       </c>
       <c r="AO129">
-        <v>121.73</v>
+        <v>0</v>
       </c>
       <c r="AP129">
         <v>0</v>
@@ -40719,16 +40719,16 @@
         <v>508.47</v>
       </c>
       <c r="AL136">
-        <v>0</v>
+        <v>45.76</v>
       </c>
       <c r="AM136">
-        <v>0</v>
+        <v>45.77</v>
       </c>
       <c r="AN136">
         <v>0</v>
       </c>
       <c r="AO136">
-        <v>91.53</v>
+        <v>0</v>
       </c>
       <c r="AP136">
         <v>0</v>
@@ -40985,16 +40985,16 @@
         <v>550.85</v>
       </c>
       <c r="AL137">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AM137">
-        <v>0</v>
+        <v>49.57000000000001</v>
       </c>
       <c r="AN137">
         <v>0</v>
       </c>
       <c r="AO137">
-        <v>99.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP137">
         <v>0</v>
@@ -41771,16 +41771,16 @@
         <v>2203.39</v>
       </c>
       <c r="AL140">
-        <v>0</v>
+        <v>198.3</v>
       </c>
       <c r="AM140">
-        <v>0</v>
+        <v>198.31</v>
       </c>
       <c r="AN140">
         <v>0</v>
       </c>
       <c r="AO140">
-        <v>396.61</v>
+        <v>0</v>
       </c>
       <c r="AP140">
         <v>0</v>
@@ -42557,16 +42557,16 @@
         <v>169.49</v>
       </c>
       <c r="AL143">
-        <v>0</v>
+        <v>15.26</v>
       </c>
       <c r="AM143">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="AN143">
         <v>0</v>
       </c>
       <c r="AO143">
-        <v>30.51</v>
+        <v>0</v>
       </c>
       <c r="AP143">
         <v>0</v>
@@ -42817,16 +42817,16 @@
         <v>550.85</v>
       </c>
       <c r="AL144">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AM144">
-        <v>0</v>
+        <v>49.57000000000001</v>
       </c>
       <c r="AN144">
         <v>0</v>
       </c>
       <c r="AO144">
-        <v>99.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP144">
         <v>0</v>
@@ -43077,16 +43077,16 @@
         <v>508.47</v>
       </c>
       <c r="AL145">
-        <v>0</v>
+        <v>45.76</v>
       </c>
       <c r="AM145">
-        <v>0</v>
+        <v>45.77</v>
       </c>
       <c r="AN145">
         <v>0</v>
       </c>
       <c r="AO145">
-        <v>91.53</v>
+        <v>0</v>
       </c>
       <c r="AP145">
         <v>0</v>
@@ -43337,16 +43337,16 @@
         <v>1271.19</v>
       </c>
       <c r="AL146">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AM146">
-        <v>0</v>
+        <v>114.41</v>
       </c>
       <c r="AN146">
         <v>0</v>
       </c>
       <c r="AO146">
-        <v>228.81</v>
+        <v>0</v>
       </c>
       <c r="AP146">
         <v>0</v>
@@ -44126,16 +44126,16 @@
         <v>676.27</v>
       </c>
       <c r="AL149">
-        <v>0</v>
+        <v>60.86</v>
       </c>
       <c r="AM149">
-        <v>0</v>
+        <v>60.87</v>
       </c>
       <c r="AN149">
         <v>0</v>
       </c>
       <c r="AO149">
-        <v>121.73</v>
+        <v>0</v>
       </c>
       <c r="AP149">
         <v>0</v>
@@ -44386,16 +44386,16 @@
         <v>1694.92</v>
       </c>
       <c r="AL150">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AM150">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AN150">
         <v>0</v>
       </c>
       <c r="AO150">
-        <v>305.08</v>
+        <v>0</v>
       </c>
       <c r="AP150">
         <v>0</v>
@@ -44912,16 +44912,16 @@
         <v>1014.41</v>
       </c>
       <c r="AL152">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="AM152">
-        <v>0</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="AN152">
         <v>0</v>
       </c>
       <c r="AO152">
-        <v>182.59</v>
+        <v>0</v>
       </c>
       <c r="AP152">
         <v>0</v>
@@ -45692,16 +45692,16 @@
         <v>2203.39</v>
       </c>
       <c r="AL155">
-        <v>0</v>
+        <v>198.3</v>
       </c>
       <c r="AM155">
-        <v>0</v>
+        <v>198.31</v>
       </c>
       <c r="AN155">
         <v>0</v>
       </c>
       <c r="AO155">
-        <v>396.61</v>
+        <v>0</v>
       </c>
       <c r="AP155">
         <v>0</v>
@@ -46732,16 +46732,16 @@
         <v>1101.69</v>
       </c>
       <c r="AL159">
-        <v>0</v>
+        <v>99.16</v>
       </c>
       <c r="AM159">
-        <v>0</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AN159">
         <v>0</v>
       </c>
       <c r="AO159">
-        <v>198.31</v>
+        <v>0</v>
       </c>
       <c r="AP159">
         <v>0</v>
@@ -46992,16 +46992,16 @@
         <v>550.85</v>
       </c>
       <c r="AL160">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AM160">
-        <v>0</v>
+        <v>49.57000000000001</v>
       </c>
       <c r="AN160">
         <v>0</v>
       </c>
       <c r="AO160">
-        <v>99.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP160">
         <v>0</v>
@@ -47252,16 +47252,16 @@
         <v>1101.69</v>
       </c>
       <c r="AL161">
-        <v>0</v>
+        <v>99.16</v>
       </c>
       <c r="AM161">
-        <v>0</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AN161">
         <v>0</v>
       </c>
       <c r="AO161">
-        <v>198.31</v>
+        <v>0</v>
       </c>
       <c r="AP161">
         <v>0</v>
@@ -47512,16 +47512,16 @@
         <v>2203.39</v>
       </c>
       <c r="AL162">
-        <v>0</v>
+        <v>198.3</v>
       </c>
       <c r="AM162">
-        <v>0</v>
+        <v>198.31</v>
       </c>
       <c r="AN162">
         <v>0</v>
       </c>
       <c r="AO162">
-        <v>396.61</v>
+        <v>0</v>
       </c>
       <c r="AP162">
         <v>0</v>
@@ -47772,16 +47772,16 @@
         <v>338.14</v>
       </c>
       <c r="AL163">
-        <v>0</v>
+        <v>30.43</v>
       </c>
       <c r="AM163">
-        <v>0</v>
+        <v>30.43</v>
       </c>
       <c r="AN163">
         <v>0</v>
       </c>
       <c r="AO163">
-        <v>60.86</v>
+        <v>0</v>
       </c>
       <c r="AP163">
         <v>0</v>
@@ -48292,16 +48292,16 @@
         <v>1271.19</v>
       </c>
       <c r="AL165">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AM165">
-        <v>0</v>
+        <v>114.41</v>
       </c>
       <c r="AN165">
         <v>0</v>
       </c>
       <c r="AO165">
-        <v>228.81</v>
+        <v>0</v>
       </c>
       <c r="AP165">
         <v>0</v>
@@ -49332,16 +49332,16 @@
         <v>338.98</v>
       </c>
       <c r="AL169">
-        <v>0</v>
+        <v>30.51</v>
       </c>
       <c r="AM169">
-        <v>0</v>
+        <v>30.51</v>
       </c>
       <c r="AN169">
         <v>0</v>
       </c>
       <c r="AO169">
-        <v>61.02</v>
+        <v>0</v>
       </c>
       <c r="AP169">
         <v>0</v>
@@ -50632,16 +50632,16 @@
         <v>508.47</v>
       </c>
       <c r="AL174">
-        <v>0</v>
+        <v>45.76</v>
       </c>
       <c r="AM174">
-        <v>0</v>
+        <v>45.77</v>
       </c>
       <c r="AN174">
         <v>0</v>
       </c>
       <c r="AO174">
-        <v>91.53</v>
+        <v>0</v>
       </c>
       <c r="AP174">
         <v>0</v>
@@ -51412,16 +51412,16 @@
         <v>847.46</v>
       </c>
       <c r="AL177">
-        <v>0</v>
+        <v>76.27</v>
       </c>
       <c r="AM177">
-        <v>0</v>
+        <v>76.27</v>
       </c>
       <c r="AN177">
         <v>0</v>
       </c>
       <c r="AO177">
-        <v>152.54</v>
+        <v>0</v>
       </c>
       <c r="AP177">
         <v>0</v>
@@ -51935,16 +51935,16 @@
         <v>847.46</v>
       </c>
       <c r="AL179">
-        <v>0</v>
+        <v>76.27</v>
       </c>
       <c r="AM179">
-        <v>0</v>
+        <v>76.27</v>
       </c>
       <c r="AN179">
         <v>0</v>
       </c>
       <c r="AO179">
-        <v>152.54</v>
+        <v>0</v>
       </c>
       <c r="AP179">
         <v>0</v>
@@ -52715,16 +52715,16 @@
         <v>677.97</v>
       </c>
       <c r="AL182">
-        <v>0</v>
+        <v>61.02</v>
       </c>
       <c r="AM182">
-        <v>0</v>
+        <v>61.01</v>
       </c>
       <c r="AN182">
         <v>0</v>
       </c>
       <c r="AO182">
-        <v>122.03</v>
+        <v>0</v>
       </c>
       <c r="AP182">
         <v>0</v>
@@ -53507,16 +53507,16 @@
         <v>169.49</v>
       </c>
       <c r="AL185">
-        <v>0</v>
+        <v>15.26</v>
       </c>
       <c r="AM185">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="AN185">
         <v>0</v>
       </c>
       <c r="AO185">
-        <v>30.51</v>
+        <v>0</v>
       </c>
       <c r="AP185">
         <v>0</v>
@@ -55339,16 +55339,16 @@
         <v>677.97</v>
       </c>
       <c r="AL192">
-        <v>0</v>
+        <v>61.02</v>
       </c>
       <c r="AM192">
-        <v>0</v>
+        <v>61.01</v>
       </c>
       <c r="AN192">
         <v>0</v>
       </c>
       <c r="AO192">
-        <v>122.03</v>
+        <v>0</v>
       </c>
       <c r="AP192">
         <v>0</v>
@@ -55859,16 +55859,16 @@
         <v>677.97</v>
       </c>
       <c r="AL194">
-        <v>0</v>
+        <v>61.02</v>
       </c>
       <c r="AM194">
-        <v>0</v>
+        <v>61.01</v>
       </c>
       <c r="AN194">
         <v>0</v>
       </c>
       <c r="AO194">
-        <v>122.03</v>
+        <v>0</v>
       </c>
       <c r="AP194">
         <v>0</v>
@@ -56639,16 +56639,16 @@
         <v>550.85</v>
       </c>
       <c r="AL197">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AM197">
-        <v>0</v>
+        <v>49.57000000000001</v>
       </c>
       <c r="AN197">
         <v>0</v>
       </c>
       <c r="AO197">
-        <v>99.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP197">
         <v>0</v>
@@ -57165,16 +57165,16 @@
         <v>423.73</v>
       </c>
       <c r="AL199">
-        <v>0</v>
+        <v>38.14</v>
       </c>
       <c r="AM199">
-        <v>0</v>
+        <v>38.13</v>
       </c>
       <c r="AN199">
         <v>0</v>
       </c>
       <c r="AO199">
-        <v>76.27</v>
+        <v>0</v>
       </c>
       <c r="AP199">
         <v>0</v>
@@ -57425,16 +57425,16 @@
         <v>1014.41</v>
       </c>
       <c r="AL200">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="AM200">
-        <v>0</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="AN200">
         <v>0</v>
       </c>
       <c r="AO200">
-        <v>182.59</v>
+        <v>0</v>
       </c>
       <c r="AP200">
         <v>0</v>
@@ -57691,16 +57691,16 @@
         <v>508.47</v>
       </c>
       <c r="AL201">
-        <v>0</v>
+        <v>45.76</v>
       </c>
       <c r="AM201">
-        <v>0</v>
+        <v>45.77</v>
       </c>
       <c r="AN201">
         <v>0</v>
       </c>
       <c r="AO201">
-        <v>91.53</v>
+        <v>0</v>
       </c>
       <c r="AP201">
         <v>0</v>
@@ -58737,16 +58737,16 @@
         <v>550.85</v>
       </c>
       <c r="AL205">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AM205">
-        <v>0</v>
+        <v>49.57000000000001</v>
       </c>
       <c r="AN205">
         <v>0</v>
       </c>
       <c r="AO205">
-        <v>99.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP205">
         <v>0</v>
@@ -59257,16 +59257,16 @@
         <v>550.85</v>
       </c>
       <c r="AL207">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AM207">
-        <v>0</v>
+        <v>49.57000000000001</v>
       </c>
       <c r="AN207">
         <v>0</v>
       </c>
       <c r="AO207">
-        <v>99.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP207">
         <v>0</v>
@@ -59783,16 +59783,16 @@
         <v>338.98</v>
       </c>
       <c r="AL209">
-        <v>0</v>
+        <v>30.51</v>
       </c>
       <c r="AM209">
-        <v>0</v>
+        <v>30.51</v>
       </c>
       <c r="AN209">
         <v>0</v>
       </c>
       <c r="AO209">
-        <v>61.02</v>
+        <v>0</v>
       </c>
       <c r="AP209">
         <v>0</v>
@@ -60043,16 +60043,16 @@
         <v>1014.41</v>
       </c>
       <c r="AL210">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="AM210">
-        <v>0</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="AN210">
         <v>0</v>
       </c>
       <c r="AO210">
-        <v>182.59</v>
+        <v>0</v>
       </c>
       <c r="AP210">
         <v>0</v>
@@ -60309,16 +60309,16 @@
         <v>1652.54</v>
       </c>
       <c r="AL211">
-        <v>0</v>
+        <v>148.73</v>
       </c>
       <c r="AM211">
-        <v>0</v>
+        <v>148.73</v>
       </c>
       <c r="AN211">
         <v>0</v>
       </c>
       <c r="AO211">
-        <v>297.46</v>
+        <v>0</v>
       </c>
       <c r="AP211">
         <v>0</v>
@@ -61349,16 +61349,16 @@
         <v>423.73</v>
       </c>
       <c r="AL215">
-        <v>0</v>
+        <v>38.14</v>
       </c>
       <c r="AM215">
-        <v>0</v>
+        <v>38.13</v>
       </c>
       <c r="AN215">
         <v>0</v>
       </c>
       <c r="AO215">
-        <v>76.27</v>
+        <v>0</v>
       </c>
       <c r="AP215">
         <v>0</v>
@@ -62909,16 +62909,16 @@
         <v>1352.54</v>
       </c>
       <c r="AL221">
-        <v>0</v>
+        <v>121.73</v>
       </c>
       <c r="AM221">
-        <v>0</v>
+        <v>121.73</v>
       </c>
       <c r="AN221">
         <v>0</v>
       </c>
       <c r="AO221">
-        <v>243.46</v>
+        <v>0</v>
       </c>
       <c r="AP221">
         <v>0</v>
@@ -63169,16 +63169,16 @@
         <v>676.27</v>
       </c>
       <c r="AL222">
-        <v>0</v>
+        <v>60.86</v>
       </c>
       <c r="AM222">
-        <v>0</v>
+        <v>60.87</v>
       </c>
       <c r="AN222">
         <v>0</v>
       </c>
       <c r="AO222">
-        <v>121.73</v>
+        <v>0</v>
       </c>
       <c r="AP222">
         <v>0</v>
@@ -63695,16 +63695,16 @@
         <v>1271.19</v>
       </c>
       <c r="AL224">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AM224">
-        <v>0</v>
+        <v>114.41</v>
       </c>
       <c r="AN224">
         <v>0</v>
       </c>
       <c r="AO224">
-        <v>228.81</v>
+        <v>0</v>
       </c>
       <c r="AP224">
         <v>0</v>
@@ -64221,16 +64221,16 @@
         <v>1352.54</v>
       </c>
       <c r="AL226">
-        <v>0</v>
+        <v>121.73</v>
       </c>
       <c r="AM226">
-        <v>0</v>
+        <v>121.73</v>
       </c>
       <c r="AN226">
         <v>0</v>
       </c>
       <c r="AO226">
-        <v>243.46</v>
+        <v>0</v>
       </c>
       <c r="AP226">
         <v>0</v>
@@ -64741,16 +64741,16 @@
         <v>423.73</v>
       </c>
       <c r="AL228">
-        <v>0</v>
+        <v>38.14</v>
       </c>
       <c r="AM228">
-        <v>0</v>
+        <v>38.13</v>
       </c>
       <c r="AN228">
         <v>0</v>
       </c>
       <c r="AO228">
-        <v>76.27</v>
+        <v>0</v>
       </c>
       <c r="AP228">
         <v>0</v>
@@ -65001,16 +65001,16 @@
         <v>1652.54</v>
       </c>
       <c r="AL229">
-        <v>0</v>
+        <v>148.73</v>
       </c>
       <c r="AM229">
-        <v>0</v>
+        <v>148.73</v>
       </c>
       <c r="AN229">
         <v>0</v>
       </c>
       <c r="AO229">
-        <v>297.46</v>
+        <v>0</v>
       </c>
       <c r="AP229">
         <v>0</v>
@@ -66313,16 +66313,16 @@
         <v>338.98</v>
       </c>
       <c r="AL234">
-        <v>0</v>
+        <v>30.51</v>
       </c>
       <c r="AM234">
-        <v>0</v>
+        <v>30.51</v>
       </c>
       <c r="AN234">
         <v>0</v>
       </c>
       <c r="AO234">
-        <v>61.02</v>
+        <v>0</v>
       </c>
       <c r="AP234">
         <v>0</v>
@@ -66839,16 +66839,16 @@
         <v>677.97</v>
       </c>
       <c r="AL236">
-        <v>0</v>
+        <v>61.02</v>
       </c>
       <c r="AM236">
-        <v>0</v>
+        <v>61.01</v>
       </c>
       <c r="AN236">
         <v>0</v>
       </c>
       <c r="AO236">
-        <v>122.03</v>
+        <v>0</v>
       </c>
       <c r="AP236">
         <v>0</v>
@@ -67359,16 +67359,16 @@
         <v>550.85</v>
       </c>
       <c r="AL238">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AM238">
-        <v>0</v>
+        <v>49.57000000000001</v>
       </c>
       <c r="AN238">
         <v>0</v>
       </c>
       <c r="AO238">
-        <v>99.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP238">
         <v>0</v>
@@ -67879,16 +67879,16 @@
         <v>1014.41</v>
       </c>
       <c r="AL240">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="AM240">
-        <v>0</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="AN240">
         <v>0</v>
       </c>
       <c r="AO240">
-        <v>182.59</v>
+        <v>0</v>
       </c>
       <c r="AP240">
         <v>0</v>
@@ -68399,16 +68399,16 @@
         <v>169.49</v>
       </c>
       <c r="AL242">
-        <v>0</v>
+        <v>15.26</v>
       </c>
       <c r="AM242">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="AN242">
         <v>0</v>
       </c>
       <c r="AO242">
-        <v>30.51</v>
+        <v>0</v>
       </c>
       <c r="AP242">
         <v>0</v>
@@ -69439,16 +69439,16 @@
         <v>1352.54</v>
       </c>
       <c r="AL246">
-        <v>0</v>
+        <v>121.73</v>
       </c>
       <c r="AM246">
-        <v>0</v>
+        <v>121.73</v>
       </c>
       <c r="AN246">
         <v>0</v>
       </c>
       <c r="AO246">
-        <v>243.46</v>
+        <v>0</v>
       </c>
       <c r="AP246">
         <v>0</v>
@@ -69959,16 +69959,16 @@
         <v>1694.92</v>
       </c>
       <c r="AL248">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AM248">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AN248">
         <v>0</v>
       </c>
       <c r="AO248">
-        <v>305.08</v>
+        <v>0</v>
       </c>
       <c r="AP248">
         <v>0</v>
@@ -70479,16 +70479,16 @@
         <v>508.47</v>
       </c>
       <c r="AL250">
-        <v>0</v>
+        <v>45.76</v>
       </c>
       <c r="AM250">
-        <v>0</v>
+        <v>45.77</v>
       </c>
       <c r="AN250">
         <v>0</v>
       </c>
       <c r="AO250">
-        <v>91.53</v>
+        <v>0</v>
       </c>
       <c r="AP250">
         <v>0</v>
@@ -70739,16 +70739,16 @@
         <v>423.73</v>
       </c>
       <c r="AL251">
-        <v>0</v>
+        <v>38.14</v>
       </c>
       <c r="AM251">
-        <v>0</v>
+        <v>38.13</v>
       </c>
       <c r="AN251">
         <v>0</v>
       </c>
       <c r="AO251">
-        <v>76.27</v>
+        <v>0</v>
       </c>
       <c r="AP251">
         <v>0</v>
@@ -73351,16 +73351,16 @@
         <v>508.47</v>
       </c>
       <c r="AL261">
-        <v>0</v>
+        <v>45.76</v>
       </c>
       <c r="AM261">
-        <v>0</v>
+        <v>45.77</v>
       </c>
       <c r="AN261">
         <v>0</v>
       </c>
       <c r="AO261">
-        <v>91.53</v>
+        <v>0</v>
       </c>
       <c r="AP261">
         <v>0</v>
@@ -73871,16 +73871,16 @@
         <v>1014.41</v>
       </c>
       <c r="AL263">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="AM263">
-        <v>0</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="AN263">
         <v>0</v>
       </c>
       <c r="AO263">
-        <v>182.59</v>
+        <v>0</v>
       </c>
       <c r="AP263">
         <v>0</v>
@@ -78055,16 +78055,16 @@
         <v>1101.69</v>
       </c>
       <c r="AL279">
-        <v>0</v>
+        <v>99.16</v>
       </c>
       <c r="AM279">
-        <v>0</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AN279">
         <v>0</v>
       </c>
       <c r="AO279">
-        <v>198.31</v>
+        <v>0</v>
       </c>
       <c r="AP279">
         <v>0</v>
@@ -79615,16 +79615,16 @@
         <v>1271.19</v>
       </c>
       <c r="AL285">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AM285">
-        <v>0</v>
+        <v>114.41</v>
       </c>
       <c r="AN285">
         <v>0</v>
       </c>
       <c r="AO285">
-        <v>228.81</v>
+        <v>0</v>
       </c>
       <c r="AP285">
         <v>0</v>
@@ -79875,16 +79875,16 @@
         <v>1101.69</v>
       </c>
       <c r="AL286">
-        <v>0</v>
+        <v>99.16</v>
       </c>
       <c r="AM286">
-        <v>0</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AN286">
         <v>0</v>
       </c>
       <c r="AO286">
-        <v>198.31</v>
+        <v>0</v>
       </c>
       <c r="AP286">
         <v>0</v>
@@ -80135,16 +80135,16 @@
         <v>423.73</v>
       </c>
       <c r="AL287">
-        <v>0</v>
+        <v>38.14</v>
       </c>
       <c r="AM287">
-        <v>0</v>
+        <v>38.13</v>
       </c>
       <c r="AN287">
         <v>0</v>
       </c>
       <c r="AO287">
-        <v>76.27</v>
+        <v>0</v>
       </c>
       <c r="AP287">
         <v>0</v>
@@ -80395,16 +80395,16 @@
         <v>1271.19</v>
       </c>
       <c r="AL288">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AM288">
-        <v>0</v>
+        <v>114.41</v>
       </c>
       <c r="AN288">
         <v>0</v>
       </c>
       <c r="AO288">
-        <v>228.81</v>
+        <v>0</v>
       </c>
       <c r="AP288">
         <v>0</v>
@@ -81447,16 +81447,16 @@
         <v>1694.92</v>
       </c>
       <c r="AL292">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AM292">
-        <v>0</v>
+        <v>152.54</v>
       </c>
       <c r="AN292">
         <v>0</v>
       </c>
       <c r="AO292">
-        <v>305.08</v>
+        <v>0</v>
       </c>
       <c r="AP292">
         <v>0</v>
@@ -81713,16 +81713,16 @@
         <v>423.73</v>
       </c>
       <c r="AL293">
-        <v>0</v>
+        <v>38.14</v>
       </c>
       <c r="AM293">
-        <v>0</v>
+        <v>38.13</v>
       </c>
       <c r="AN293">
         <v>0</v>
       </c>
       <c r="AO293">
-        <v>76.27</v>
+        <v>0</v>
       </c>
       <c r="AP293">
         <v>0</v>
@@ -82499,16 +82499,16 @@
         <v>676.27</v>
       </c>
       <c r="AL296">
-        <v>0</v>
+        <v>60.86</v>
       </c>
       <c r="AM296">
-        <v>0</v>
+        <v>60.87</v>
       </c>
       <c r="AN296">
         <v>0</v>
       </c>
       <c r="AO296">
-        <v>121.73</v>
+        <v>0</v>
       </c>
       <c r="AP296">
         <v>0</v>
@@ -82765,16 +82765,16 @@
         <v>2203.39</v>
       </c>
       <c r="AL297">
-        <v>0</v>
+        <v>198.3</v>
       </c>
       <c r="AM297">
-        <v>0</v>
+        <v>198.31</v>
       </c>
       <c r="AN297">
         <v>0</v>
       </c>
       <c r="AO297">
-        <v>396.61</v>
+        <v>0</v>
       </c>
       <c r="AP297">
         <v>0</v>
@@ -83557,16 +83557,16 @@
         <v>1652.54</v>
       </c>
       <c r="AL300">
-        <v>0</v>
+        <v>148.73</v>
       </c>
       <c r="AM300">
-        <v>0</v>
+        <v>148.73</v>
       </c>
       <c r="AN300">
         <v>0</v>
       </c>
       <c r="AO300">
-        <v>297.46</v>
+        <v>0</v>
       </c>
       <c r="AP300">
         <v>0</v>
@@ -83817,16 +83817,16 @@
         <v>1014.41</v>
       </c>
       <c r="AL301">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="AM301">
-        <v>0</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="AN301">
         <v>0</v>
       </c>
       <c r="AO301">
-        <v>182.59</v>
+        <v>0</v>
       </c>
       <c r="AP301">
         <v>0</v>
